--- a/artfynd/A 35930-2024 artfynd.xlsx
+++ b/artfynd/A 35930-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071459</v>
+        <v>120071549</v>
       </c>
       <c r="B2" t="n">
-        <v>90582</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597286</v>
+        <v>597215</v>
       </c>
       <c r="R2" t="n">
-        <v>6383097</v>
+        <v>6383110</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071549</v>
+        <v>120071459</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,13 +837,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597215</v>
+        <v>597286</v>
       </c>
       <c r="R3" t="n">
-        <v>6383110</v>
+        <v>6383097</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,6 +904,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35930-2024 artfynd.xlsx
+++ b/artfynd/A 35930-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071549</v>
+        <v>120071459</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597215</v>
+        <v>597286</v>
       </c>
       <c r="R2" t="n">
-        <v>6383110</v>
+        <v>6383097</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,6 +780,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071459</v>
+        <v>120071549</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,12 +837,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597286</v>
+        <v>597215</v>
       </c>
       <c r="R3" t="n">
-        <v>6383097</v>
+        <v>6383110</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,7 +905,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35930-2024 artfynd.xlsx
+++ b/artfynd/A 35930-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120071459</v>
+        <v>120071549</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597286</v>
+        <v>597215</v>
       </c>
       <c r="R2" t="n">
-        <v>6383097</v>
+        <v>6383110</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120071549</v>
+        <v>120071459</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,13 +837,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597215</v>
+        <v>597286</v>
       </c>
       <c r="R3" t="n">
-        <v>6383110</v>
+        <v>6383097</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,6 +904,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
